--- a/2_SQL_database/Data_clean_updated/MCAS/Estados_US/Edos_USA_2010/FLORIDA_2010.xlsx
+++ b/2_SQL_database/Data_clean_updated/MCAS/Estados_US/Edos_USA_2010/FLORIDA_2010.xlsx
@@ -2958,7 +2958,7 @@
       </c>
       <c r="B145" t="inlineStr">
         <is>
-          <t>Temosachi</t>
+          <t>Temosachic</t>
         </is>
       </c>
       <c r="C145">
@@ -3840,7 +3840,7 @@
       </c>
       <c r="B194" t="inlineStr">
         <is>
-          <t>Gral. Simon Boivar</t>
+          <t>Gral. Simon Bolivar</t>
         </is>
       </c>
       <c r="C194">
@@ -4308,7 +4308,7 @@
       </c>
       <c r="B220" t="inlineStr">
         <is>
-          <t>Allende</t>
+          <t>San Miguel De Allende</t>
         </is>
       </c>
       <c r="C220">
@@ -13560,7 +13560,7 @@
       </c>
       <c r="B734" t="inlineStr">
         <is>
-          <t>Dr. Arroyo</t>
+          <t>Doctor Arroyo</t>
         </is>
       </c>
       <c r="C734">
@@ -15468,7 +15468,7 @@
       </c>
       <c r="B840" t="inlineStr">
         <is>
-          <t>San Juan Mixtepec - Distr. 08 -</t>
+          <t>San Juan Mixtepec -Dto. 08 -</t>
         </is>
       </c>
       <c r="C840">
@@ -15486,7 +15486,7 @@
       </c>
       <c r="B841" t="inlineStr">
         <is>
-          <t>San Juan Mixtepec - Distr. 26 -</t>
+          <t>San Juan Mixtepec -Dto. 26 -</t>
         </is>
       </c>
       <c r="C841">
@@ -16260,7 +16260,7 @@
       </c>
       <c r="B884" t="inlineStr">
         <is>
-          <t>San Pedro Mixtepec - Distr. 22 -</t>
+          <t>San Pedro Mixtepec -Dto. 22 -</t>
         </is>
       </c>
       <c r="C884">
@@ -16278,7 +16278,7 @@
       </c>
       <c r="B885" t="inlineStr">
         <is>
-          <t>San Pedro Mixtepec - Distr. 26 -</t>
+          <t>San Pedro Mixtepec -Dto. 26 -</t>
         </is>
       </c>
       <c r="C885">
@@ -23370,7 +23370,7 @@
       </c>
       <c r="B1279" t="inlineStr">
         <is>
-          <t>Altzayanca</t>
+          <t>Atltzayanca</t>
         </is>
       </c>
       <c r="C1279">
@@ -23820,7 +23820,7 @@
       </c>
       <c r="B1304" t="inlineStr">
         <is>
-          <t>Yauhquemecan</t>
+          <t>Yauhquemehcan</t>
         </is>
       </c>
       <c r="C1304">
@@ -26556,7 +26556,7 @@
       </c>
       <c r="B1456" t="inlineStr">
         <is>
-          <t>Tuxpam</t>
+          <t>Tuxpan</t>
         </is>
       </c>
       <c r="C1456">
